--- a/data/trans_orig/P36B17-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B17-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>59261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40342</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>90450</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>75286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>105622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>70367</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>55101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88746</t>
+          <t>86078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73891</t>
+          <t>85446</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61864</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86585</t>
+          <t>99413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>155813</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122347</t>
+          <t>137450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166032</t>
+          <t>178279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>204155</t>
+          <t>200290</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183918</t>
+          <t>183719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223616</t>
+          <t>218185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>169865</t>
+          <t>181940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155407</t>
+          <t>166987</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>183707</t>
+          <t>195724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>374020</t>
+          <t>382230</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>349974</t>
+          <t>358612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>398110</t>
+          <t>405487</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86416</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65944</t>
+          <t>66477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109174</t>
+          <t>108309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>92817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74211</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>108453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>173991</t>
+          <t>178816</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>151628</t>
+          <t>153928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204031</t>
+          <t>203748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>168107</t>
+          <t>173815</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140350</t>
+          <t>150224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194607</t>
+          <t>203367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>194142</t>
+          <t>204086</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176189</t>
+          <t>184542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214762</t>
+          <t>225394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>362249</t>
+          <t>377900</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328734</t>
+          <t>344997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>394990</t>
+          <t>413552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>220909</t>
+          <t>227748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190771</t>
+          <t>196460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>251786</t>
+          <t>255716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200055</t>
+          <t>213971</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179366</t>
+          <t>193572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220340</t>
+          <t>236467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>420964</t>
+          <t>441719</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385275</t>
+          <t>408951</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>456513</t>
+          <t>481130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1746,102 +1746,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>43085</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>67187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>32854</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23984</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>44115</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>75939</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>60114</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>97273</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30456</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>21516</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>41907</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>73414</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>56735</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>99963</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1894,27 +1894,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>104740</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121323</t>
+          <t>123538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>141789</t>
+          <t>146557</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126699</t>
+          <t>131628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157263</t>
+          <t>162863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>246529</t>
+          <t>253160</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225429</t>
+          <t>232125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269406</t>
+          <t>274547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>85430</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72089</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102807</t>
+          <t>101753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>99379</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82872</t>
+          <t>85063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110933</t>
+          <t>114456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>183833</t>
+          <t>184809</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>159815</t>
+          <t>165118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>205770</t>
+          <t>206377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96240</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79760</t>
+          <t>78828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>110872</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80136</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67480</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93438</t>
+          <t>95736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>176376</t>
+          <t>174729</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156697</t>
+          <t>155530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>198691</t>
+          <t>195807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>45079</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>32778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>313257</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313257</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>313257</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>341723</t>
+          <t>351209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>341723</t>
+          <t>351209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>341723</t>
+          <t>351209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>654980</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>654980</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>654980</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71706</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56302</t>
+          <t>63104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89653</t>
+          <t>103090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>104310</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>91383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116954</t>
+          <t>123163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>161959</t>
+          <t>185643</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>160580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>193030</t>
+          <t>209577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>112928</t>
+          <t>133356</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>109725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134422</t>
+          <t>158407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>144849</t>
+          <t>159741</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91267</t>
+          <t>140705</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186576</t>
+          <t>177761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>257777</t>
+          <t>293097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185244</t>
+          <t>262782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>304862</t>
+          <t>323273</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105539</t>
+          <t>136724</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84154</t>
+          <t>111918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126994</t>
+          <t>163090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>219462</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>152842</t>
+          <t>114498</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>323171</t>
+          <t>152028</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>325001</t>
+          <t>269620</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>258945</t>
+          <t>239936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>457327</t>
+          <t>302890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>41116</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65642</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311799</t>
+          <t>372348</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>311799</t>
+          <t>372348</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311799</t>
+          <t>372348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>473809</t>
+          <t>418185</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>473809</t>
+          <t>418185</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>473809</t>
+          <t>418185</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>785609</t>
+          <t>790533</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>785609</t>
+          <t>790533</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>785609</t>
+          <t>790533</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38710</t>
+          <t>43636</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>54123</t>
+          <t>59761</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>50691</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62878</t>
+          <t>69215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>102689</t>
+          <t>113993</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115654</t>
+          <t>127935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>106966</t>
+          <t>125478</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>95636</t>
+          <t>111742</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118511</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>137967</t>
+          <t>149549</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128451</t>
+          <t>138380</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147847</t>
+          <t>159845</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>244933</t>
+          <t>275028</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230192</t>
+          <t>258902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259349</t>
+          <t>292233</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25596</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43753</t>
+          <t>48241</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>738</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>738</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>84237</t>
+          <t>87549</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71240</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>111023</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>94426</t>
+          <t>97100</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>118350</t>
+          <t>124243</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>190972</t>
+          <t>198572</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>173063</t>
+          <t>179610</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>208673</t>
+          <t>214656</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>86017</t>
+          <t>86870</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>73936</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>101192</t>
+          <t>99926</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>99505</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>86143</t>
+          <t>87075</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>111324</t>
+          <t>113262</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>184285</t>
+          <t>186375</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>166074</t>
+          <t>169006</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>205665</t>
+          <t>205350</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>77477</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>65147</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>94522</t>
+          <t>91552</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>42311</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>55068</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>121776</t>
+          <t>120871</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>104388</t>
+          <t>105040</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>140938</t>
+          <t>139027</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37012</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>245683</t>
+          <t>285912</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>216475</t>
+          <t>252993</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>271928</t>
+          <t>315818</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>474629</t>
+          <t>325124</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>344703</t>
+          <t>300015</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>661789</t>
+          <t>351096</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>720311</t>
+          <t>611035</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>583215</t>
+          <t>570307</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1028339</t>
+          <t>648240</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>196259</t>
+          <t>232963</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>169914</t>
+          <t>206444</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>222229</t>
+          <t>263789</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>207281</t>
+          <t>245152</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>219737</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>284779</t>
+          <t>272133</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>403540</t>
+          <t>478115</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>253271</t>
+          <t>441213</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>485049</t>
+          <t>516512</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>130351</t>
+          <t>140553</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>105729</t>
+          <t>117723</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>157892</t>
+          <t>168554</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>131181</t>
+          <t>159447</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>137407</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>183118</t>
+          <t>182956</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>261531</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>142743</t>
+          <t>267590</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>316085</t>
+          <t>338751</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>67665</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>64983</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>40730</t>
+          <t>57676</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>89075</t>
+          <t>97489</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>26119</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>39802</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>623445</t>
+          <t>718842</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>623445</t>
+          <t>718842</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>623445</t>
+          <t>718842</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>847815</t>
+          <t>770481</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1471260</t>
+          <t>1489323</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1471260</t>
+          <t>1489323</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1471260</t>
+          <t>1489323</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>143803</t>
+          <t>168222</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>144748</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>204672</t>
+          <t>192800</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>185346</t>
+          <t>216146</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>164010</t>
+          <t>196394</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>205336</t>
+          <t>240225</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>329149</t>
+          <t>384368</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>205770</t>
+          <t>352630</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>397381</t>
+          <t>417166</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>190408</t>
+          <t>220873</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>88862</t>
+          <t>195667</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>268471</t>
+          <t>247961</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>249154</t>
+          <t>287803</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>227600</t>
+          <t>263051</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>269963</t>
+          <t>311491</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>439562</t>
+          <t>508676</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>280375</t>
+          <t>473578</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>529327</t>
+          <t>547494</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>213351</t>
+          <t>250045</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>222850</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>299687</t>
+          <t>276786</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>206462</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>186414</t>
+          <t>213120</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>226988</t>
+          <t>260086</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>419814</t>
+          <t>485094</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>247163</t>
+          <t>449173</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>503716</t>
+          <t>521444</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>90874</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>118564</t>
+          <t>114534</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>50310</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>81271</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>134582</t>
+          <t>156441</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>85859</t>
+          <t>131254</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>169832</t>
+          <t>181602</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>300971</t>
+          <t>68058</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>636426</t>
+          <t>89475</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>15612</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>323346</t>
+          <t>94824</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>86574</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>818290</t>
+          <t>122717</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>820511</t>
+          <t>916089</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>617626</t>
+          <t>860785</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>901733</t>
+          <t>971510</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>1180791</t>
+          <t>1099948</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1009632</t>
+          <t>1050639</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1640024</t>
+          <t>1150676</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2001302</t>
+          <t>2016037</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1799354</t>
+          <t>1948160</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2427695</t>
+          <t>2091280</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1017634</t>
+          <t>1129153</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>758741</t>
+          <t>1068265</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1118444</t>
+          <t>1184929</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1202105</t>
+          <t>1330663</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1283771</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1303542</t>
+          <t>1384538</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2219740</t>
+          <t>2459816</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1935533</t>
+          <t>2385739</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2373973</t>
+          <t>2546057</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1069325</t>
+          <t>1148391</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>810350</t>
+          <t>1091079</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1167781</t>
+          <t>1215568</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1062957</t>
+          <t>1062408</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>889481</t>
+          <t>1005997</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1215676</t>
+          <t>1111050</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2132282</t>
+          <t>2210799</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1876472</t>
+          <t>2122245</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2314624</t>
+          <t>2299833</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>227669</t>
+          <t>246721</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>182622</t>
+          <t>209791</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>271996</t>
+          <t>285239</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>180400</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>127510</t>
+          <t>158063</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>187599</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>389448</t>
+          <t>427120</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>326619</t>
+          <t>379351</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>440276</t>
+          <t>472869</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>320293</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1087171</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>66691</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>363673</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>114201</t>
+          <t>116279</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1198403</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
